--- a/Result/checksun_type/電動車.xlsx
+++ b/Result/checksun_type/電動車.xlsx
@@ -641,62 +641,62 @@
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>my_signal</t>
+          <t>up_up</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>my_signal_3d</t>
+          <t>up_up_3d</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>my_signal_5d</t>
+          <t>up_up_5d</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>my_signal_10d</t>
+          <t>up_up_10d</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>up_up</t>
+          <t>bbw_cross</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>up_up_3d</t>
+          <t>MA_UP_d</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>up_up_5d</t>
+          <t>MA_UP_3d</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>up_up_10d</t>
+          <t>MA_UP_5d</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>bbw_cross</t>
+          <t>MA_UP_10d</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>MA_UP_3d</t>
+          <t>MA_UP_20d</t>
         </is>
       </c>
       <c r="BA1" s="1" t="inlineStr">
         <is>
-          <t>MA_UP_5d</t>
+          <t>MA_UP_30d</t>
         </is>
       </c>
       <c r="BB1" s="1" t="inlineStr">
         <is>
-          <t>MA_UP_10d</t>
+          <t>MA_UP_40d</t>
         </is>
       </c>
       <c r="BC1" s="1" t="inlineStr">
@@ -1653,52 +1653,52 @@
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
@@ -1893,11 +1893,15 @@
           <t>2358.0</t>
         </is>
       </c>
-      <c r="CQ2" t="n">
-        <v>2177</v>
-      </c>
-      <c r="CR2" t="n">
-        <v>2179.3</v>
+      <c r="CQ2" t="inlineStr">
+        <is>
+          <t>2177.0</t>
+        </is>
+      </c>
+      <c r="CR2" t="inlineStr">
+        <is>
+          <t>2179.3</t>
+        </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
@@ -2013,7 +2017,7 @@
       </c>
       <c r="DQ2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="DR2" t="inlineStr">
@@ -2635,52 +2639,52 @@
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
@@ -2875,11 +2879,15 @@
           <t>2303.5</t>
         </is>
       </c>
-      <c r="CQ3" t="n">
-        <v>2158.5</v>
-      </c>
-      <c r="CR3" t="n">
-        <v>2170.8</v>
+      <c r="CQ3" t="inlineStr">
+        <is>
+          <t>2158.5</t>
+        </is>
+      </c>
+      <c r="CR3" t="inlineStr">
+        <is>
+          <t>2170.8</t>
+        </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
@@ -2995,7 +3003,7 @@
       </c>
       <c r="DQ3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="DR3" t="inlineStr">
@@ -3612,27 +3620,27 @@
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
@@ -3642,27 +3650,27 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
@@ -3857,11 +3865,15 @@
           <t>2246.0</t>
         </is>
       </c>
-      <c r="CQ4" t="n">
-        <v>2146.5</v>
-      </c>
-      <c r="CR4" t="n">
-        <v>2159.7</v>
+      <c r="CQ4" t="inlineStr">
+        <is>
+          <t>2146.5</t>
+        </is>
+      </c>
+      <c r="CR4" t="inlineStr">
+        <is>
+          <t>2159.7</t>
+        </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
@@ -3977,7 +3989,7 @@
       </c>
       <c r="DQ4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="DR4" t="inlineStr">
@@ -4594,57 +4606,57 @@
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
@@ -4839,11 +4851,15 @@
           <t>2182.0</t>
         </is>
       </c>
-      <c r="CQ5" t="n">
-        <v>2125.25</v>
-      </c>
-      <c r="CR5" t="n">
-        <v>2144.2</v>
+      <c r="CQ5" t="inlineStr">
+        <is>
+          <t>2125.25</t>
+        </is>
+      </c>
+      <c r="CR5" t="inlineStr">
+        <is>
+          <t>2144.2</t>
+        </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
@@ -4959,7 +4975,7 @@
       </c>
       <c r="DQ5" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="DR5" t="inlineStr">
@@ -5571,22 +5587,22 @@
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -5596,37 +5612,37 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AW6" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
+      <c r="AY6" t="inlineStr">
         <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
@@ -5821,11 +5837,15 @@
           <t>2125.0</t>
         </is>
       </c>
-      <c r="CQ6" t="n">
-        <v>2116</v>
-      </c>
-      <c r="CR6" t="n">
-        <v>2130.6</v>
+      <c r="CQ6" t="inlineStr">
+        <is>
+          <t>2116.0</t>
+        </is>
+      </c>
+      <c r="CR6" t="inlineStr">
+        <is>
+          <t>2130.6</t>
+        </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
@@ -6553,22 +6573,22 @@
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -6578,24 +6598,24 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AW7" t="inlineStr">
+      <c r="AX7" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
+      <c r="AY7" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
       <c r="AZ7" t="inlineStr">
         <is>
           <t>3.0</t>
@@ -6603,12 +6623,12 @@
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
@@ -6803,11 +6823,15 @@
           <t>2084.0</t>
         </is>
       </c>
-      <c r="CQ7" t="n">
-        <v>2101.75</v>
-      </c>
-      <c r="CR7" t="n">
-        <v>2122.9</v>
+      <c r="CQ7" t="inlineStr">
+        <is>
+          <t>2101.75</t>
+        </is>
+      </c>
+      <c r="CR7" t="inlineStr">
+        <is>
+          <t>2122.9</t>
+        </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
@@ -7535,22 +7559,22 @@
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -7560,24 +7584,24 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AW8" t="inlineStr">
+      <c r="AX8" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
+      <c r="AY8" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
       <c r="AZ8" t="inlineStr">
         <is>
           <t>2.0</t>
@@ -7585,12 +7609,12 @@
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
@@ -7785,11 +7809,15 @@
           <t>2047.5</t>
         </is>
       </c>
-      <c r="CQ8" t="n">
-        <v>2085</v>
-      </c>
-      <c r="CR8" t="n">
-        <v>2114.3</v>
+      <c r="CQ8" t="inlineStr">
+        <is>
+          <t>2085.0</t>
+        </is>
+      </c>
+      <c r="CR8" t="inlineStr">
+        <is>
+          <t>2114.3</t>
+        </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
@@ -8517,22 +8545,22 @@
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -8542,24 +8570,24 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AW9" t="inlineStr">
+      <c r="AX9" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
+      <c r="AY9" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
       <c r="AZ9" t="inlineStr">
         <is>
           <t>1.0</t>
@@ -8567,12 +8595,12 @@
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
@@ -8767,11 +8795,15 @@
           <t>2016.5</t>
         </is>
       </c>
-      <c r="CQ9" t="n">
-        <v>2076.5</v>
-      </c>
-      <c r="CR9" t="n">
-        <v>2104.9</v>
+      <c r="CQ9" t="inlineStr">
+        <is>
+          <t>2076.5</t>
+        </is>
+      </c>
+      <c r="CR9" t="inlineStr">
+        <is>
+          <t>2104.9</t>
+        </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
@@ -9519,12 +9551,12 @@
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
@@ -9539,7 +9571,7 @@
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
@@ -9549,12 +9581,12 @@
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
@@ -9749,11 +9781,15 @@
           <t>1993.5</t>
         </is>
       </c>
-      <c r="CQ10" t="n">
-        <v>2064</v>
-      </c>
-      <c r="CR10" t="n">
-        <v>2096.2</v>
+      <c r="CQ10" t="inlineStr">
+        <is>
+          <t>2064.0</t>
+        </is>
+      </c>
+      <c r="CR10" t="inlineStr">
+        <is>
+          <t>2096.2</t>
+        </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
@@ -10506,7 +10542,7 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
@@ -10521,7 +10557,7 @@
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
@@ -10731,11 +10767,15 @@
           <t>46.61499999999999</t>
         </is>
       </c>
-      <c r="CQ11" t="n">
-        <v>47.21</v>
-      </c>
-      <c r="CR11" t="n">
-        <v>48.83</v>
+      <c r="CQ11" t="inlineStr">
+        <is>
+          <t>47.21</t>
+        </is>
+      </c>
+      <c r="CR11" t="inlineStr">
+        <is>
+          <t>48.83</t>
+        </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
@@ -11488,7 +11528,7 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
@@ -11503,7 +11543,7 @@
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
@@ -11713,11 +11753,15 @@
           <t>46.575</t>
         </is>
       </c>
-      <c r="CQ12" t="n">
-        <v>47.36</v>
-      </c>
-      <c r="CR12" t="n">
-        <v>48.95</v>
+      <c r="CQ12" t="inlineStr">
+        <is>
+          <t>47.36</t>
+        </is>
+      </c>
+      <c r="CR12" t="inlineStr">
+        <is>
+          <t>48.95</t>
+        </is>
       </c>
       <c r="CS12" t="inlineStr">
         <is>
@@ -12470,7 +12514,7 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
@@ -12485,7 +12529,7 @@
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
@@ -12695,11 +12739,15 @@
           <t>46.51</t>
         </is>
       </c>
-      <c r="CQ13" t="n">
-        <v>47.49</v>
-      </c>
-      <c r="CR13" t="n">
-        <v>49.02</v>
+      <c r="CQ13" t="inlineStr">
+        <is>
+          <t>47.49</t>
+        </is>
+      </c>
+      <c r="CR13" t="inlineStr">
+        <is>
+          <t>49.02</t>
+        </is>
       </c>
       <c r="CS13" t="inlineStr">
         <is>
@@ -13452,7 +13500,7 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
@@ -13467,7 +13515,7 @@
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
@@ -13677,11 +13725,15 @@
           <t>46.505</t>
         </is>
       </c>
-      <c r="CQ14" t="n">
-        <v>47.63</v>
-      </c>
-      <c r="CR14" t="n">
-        <v>49.07</v>
+      <c r="CQ14" t="inlineStr">
+        <is>
+          <t>47.63</t>
+        </is>
+      </c>
+      <c r="CR14" t="inlineStr">
+        <is>
+          <t>49.07</t>
+        </is>
       </c>
       <c r="CS14" t="inlineStr">
         <is>
@@ -14434,7 +14486,7 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
@@ -14449,7 +14501,7 @@
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
@@ -14659,11 +14711,15 @@
           <t>46.585</t>
         </is>
       </c>
-      <c r="CQ15" t="n">
-        <v>47.82</v>
-      </c>
-      <c r="CR15" t="n">
-        <v>49.13</v>
+      <c r="CQ15" t="inlineStr">
+        <is>
+          <t>47.82</t>
+        </is>
+      </c>
+      <c r="CR15" t="inlineStr">
+        <is>
+          <t>49.13</t>
+        </is>
       </c>
       <c r="CS15" t="inlineStr">
         <is>
@@ -15416,7 +15472,7 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
@@ -15431,7 +15487,7 @@
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
@@ -15641,11 +15697,15 @@
           <t>46.665</t>
         </is>
       </c>
-      <c r="CQ16" t="n">
-        <v>48.02</v>
-      </c>
-      <c r="CR16" t="n">
-        <v>49.25</v>
+      <c r="CQ16" t="inlineStr">
+        <is>
+          <t>48.02</t>
+        </is>
+      </c>
+      <c r="CR16" t="inlineStr">
+        <is>
+          <t>49.25</t>
+        </is>
       </c>
       <c r="CS16" t="inlineStr">
         <is>
@@ -16398,7 +16458,7 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
@@ -16413,7 +16473,7 @@
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
@@ -16623,11 +16683,15 @@
           <t>46.83499999999999</t>
         </is>
       </c>
-      <c r="CQ17" t="n">
-        <v>48.21</v>
-      </c>
-      <c r="CR17" t="n">
-        <v>49.38</v>
+      <c r="CQ17" t="inlineStr">
+        <is>
+          <t>48.21</t>
+        </is>
+      </c>
+      <c r="CR17" t="inlineStr">
+        <is>
+          <t>49.38</t>
+        </is>
       </c>
       <c r="CS17" t="inlineStr">
         <is>
@@ -17380,7 +17444,7 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
@@ -17395,7 +17459,7 @@
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
@@ -17605,11 +17669,15 @@
           <t>46.99</t>
         </is>
       </c>
-      <c r="CQ18" t="n">
-        <v>48.37</v>
-      </c>
-      <c r="CR18" t="n">
-        <v>49.52</v>
+      <c r="CQ18" t="inlineStr">
+        <is>
+          <t>48.37</t>
+        </is>
+      </c>
+      <c r="CR18" t="inlineStr">
+        <is>
+          <t>49.52</t>
+        </is>
       </c>
       <c r="CS18" t="inlineStr">
         <is>
@@ -18362,7 +18430,7 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
@@ -18377,7 +18445,7 @@
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
@@ -18587,11 +18655,15 @@
           <t>47.21</t>
         </is>
       </c>
-      <c r="CQ19" t="n">
-        <v>48.49</v>
-      </c>
-      <c r="CR19" t="n">
-        <v>49.71</v>
+      <c r="CQ19" t="inlineStr">
+        <is>
+          <t>48.49</t>
+        </is>
+      </c>
+      <c r="CR19" t="inlineStr">
+        <is>
+          <t>49.71</t>
+        </is>
       </c>
       <c r="CS19" t="inlineStr">
         <is>
